--- a/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-24.xlsx
+++ b/Operacional/clientes/construmais/outputs/10-2026/Arquivos/14-disparo-whatsapp/14-disparo-whatsapp-lote-24.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="22.63" customWidth="1" style="3" min="1" max="1"/>
@@ -474,259 +474,514 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
-        <v>5581991607188</v>
+        <v>5554999560047</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Evandro</t>
+          <t>G.p.a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Evandro Oliveira</t>
+          <t>G.P.A Gerenciamento</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
-        <v>5583991024267</v>
+        <v>5583987153391</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Luiz</t>
+          <t>Rodrigo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Luiz Henrique Domingos da Silva</t>
+          <t>Rodrigo Diniz</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>5583981022335</v>
+        <v>5583991576868</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jailton</t>
+          <t>Drogaria</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jailton Soares</t>
+          <t>Drogaria Equilibrio</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>5583987653028</v>
+        <v>5583999567557</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Kaio</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jose Francisco da Silva Filho</t>
+          <t>Kaio Pacifico Soares Formiga</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>5583986212552</v>
+        <v>5583988341845</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Augusto</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Augusto Saldanha Woellner</t>
+          <t>Ana Maria Alves da Silva Barbosa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>5583993050090</v>
+        <v>5583993131962</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ricardo</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Maria do Socorro Rodrigues</t>
+          <t>Ricardo Lourenço</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5583987693897</v>
+        <v>5598984820048</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Escola</t>
+          <t>Talony</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Escola Municipal Prof Agostinho Fonseca Neto</t>
+          <t>Talony Poljean Alves de Araujo</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>5583999522633</v>
+        <v>5583987990918</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Marinsberg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Tulio</t>
+          <t>Marinsberg Ramos de Oliveira</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>5583987540378</v>
+        <v>5583988354449</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ramon</t>
+          <t>Rigoberto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ramon Santana Lopes</t>
+          <t>Rigoberto Araujo Pereira</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>5583999839681</v>
+        <v>5583986397104</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Valdineia</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Valdineia Mariz</t>
+          <t>Maria de Lourdes Silva Amorim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>5583987223840</v>
+        <v>5583986016509</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vania</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vania Maria Pereira da Silva</t>
+          <t>Charles Philip Orfeo Nobrega Osias</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5583993255368</v>
+        <v>5583988379222</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Damiao</t>
+          <t>Vania</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Damiao Fernando dos Santos</t>
+          <t>Vania de Lima Araujo</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>5583987530120</v>
+        <v>5571996450615</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Antonio Carneiro</t>
+          <t>Jean Carlo Miranda Monteiro</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>5583991537878</v>
+        <v>5583998164584</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jonata</t>
+          <t>Eduardo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonata de Souza Araujo</t>
+          <t>Eduardo da Silva</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>5583991375144</v>
+        <v>5583996255574</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jorcelina</t>
+          <t>Rommel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jorcelina Rodrigues Vieira da Silva</t>
+          <t>Rommel Lucena</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
+        <v>5583986498556</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Antonio</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Antonio Goncalves da Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>5583987159983</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Elis</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Elis Regina de Souza</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>5583986471786</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kaline</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Kaline Felipe Martins</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>5581991607188</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Evandro</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Evandro Oliveira</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="3">
+      <c r="A21" s="4" t="n">
+        <v>5583991024267</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Luiz</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Luiz Henrique Domingos da Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="3">
+      <c r="A22" s="4" t="n">
+        <v>5583981022335</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jailton</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Jailton Soares</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="3">
+      <c r="A23" s="4" t="n">
+        <v>5583987653028</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Jose Francisco da Silva Filho</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="3">
+      <c r="A24" s="4" t="n">
+        <v>5583986212552</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Augusto</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Augusto Saldanha Woellner</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="3">
+      <c r="A25" s="4" t="n">
+        <v>5583993050090</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Maria do Socorro Rodrigues</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="3">
+      <c r="A26" s="4" t="n">
+        <v>5583987693897</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Escola</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Escola Municipal Prof Agostinho Fonseca Neto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" s="3">
+      <c r="A27" s="4" t="n">
+        <v>5583999522633</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Jose</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Jose Tulio</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" s="3">
+      <c r="A28" s="4" t="n">
+        <v>5583987540378</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ramon</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ramon Santana Lopes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" s="3">
+      <c r="A29" s="4" t="n">
+        <v>5583999839681</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Valdineia</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Valdineia Mariz</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="3">
+      <c r="A30" s="4" t="n">
+        <v>5583987223840</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vania</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Vania Maria Pereira da Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" s="3">
+      <c r="A31" s="4" t="n">
+        <v>5583993255368</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Damiao</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Damiao Fernando dos Santos</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" s="3">
+      <c r="A32" s="4" t="n">
+        <v>5583987530120</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Antonio</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Antonio Carneiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" s="3">
+      <c r="A33" s="4" t="n">
+        <v>5583991537878</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Jonata</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jonata de Souza Araujo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" s="3">
+      <c r="A34" s="4" t="n">
+        <v>5583991375144</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Jorcelina</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jorcelina Rodrigues Vieira da Silva</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1" s="3">
+      <c r="A35" s="4" t="n">
         <v>5583988070662</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>Jose</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Jose Rosildo Farias</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="3"/>
-    <row r="22" ht="15.75" customHeight="1" s="3"/>
-    <row r="23" ht="15.75" customHeight="1" s="3"/>
-    <row r="24" ht="15.75" customHeight="1" s="3"/>
-    <row r="25" ht="15.75" customHeight="1" s="3"/>
-    <row r="26" ht="15.75" customHeight="1" s="3"/>
-    <row r="27" ht="15.75" customHeight="1" s="3"/>
-    <row r="28" ht="15.75" customHeight="1" s="3"/>
-    <row r="29" ht="15.75" customHeight="1" s="3"/>
-    <row r="30" ht="15.75" customHeight="1" s="3"/>
-    <row r="31" ht="15.75" customHeight="1" s="3"/>
-    <row r="32" ht="15.75" customHeight="1" s="3"/>
-    <row r="33" ht="15.75" customHeight="1" s="3"/>
-    <row r="34" ht="15.75" customHeight="1" s="3"/>
-    <row r="35" ht="15.75" customHeight="1" s="3"/>
     <row r="36" ht="15.75" customHeight="1" s="3"/>
     <row r="37" ht="15.75" customHeight="1" s="3"/>
     <row r="38" ht="15.75" customHeight="1" s="3"/>
